--- a/Field_Elevate_Sector_Monthly_Returns.xlsx
+++ b/Field_Elevate_Sector_Monthly_Returns.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5887,7 +5887,6 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>6.25</v>
       </c>
@@ -5930,6 +5929,57 @@
       </c>
       <c r="O109" t="n">
         <v>-2.82</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="n">
+        <v>-14.58</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Crypto &amp; Digital Assets</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>

--- a/Field_Elevate_Sector_Monthly_Returns.xlsx
+++ b/Field_Elevate_Sector_Monthly_Returns.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monthly" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5937,7 +5937,6 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>-14.58</v>
       </c>
@@ -5980,6 +5979,57 @@
       </c>
       <c r="O110" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="D111" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E111" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="F111" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I111" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="J111" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="K111" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Crypto &amp; Digital Assets</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Precious Metals</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
+        <v>7.45</v>
       </c>
     </row>
   </sheetData>

--- a/Field_Elevate_Sector_Monthly_Returns.xlsx
+++ b/Field_Elevate_Sector_Monthly_Returns.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5987,7 +5987,6 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
         <v>3.79</v>
       </c>
@@ -6030,6 +6029,57 @@
       </c>
       <c r="O111" t="n">
         <v>7.45</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-7.77</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="F112" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-5.68</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="J112" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Tech &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Crypto &amp; Digital Assets</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>-2.07</v>
       </c>
     </row>
   </sheetData>
